--- a/data/trending_integrated_20261008_09.xlsx
+++ b/data/trending_integrated_20261008_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1733000</v>
+        <v>60500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+0.58%</t>
+          <t>'+4.13%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.12</v>
+        <v>0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>496</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
-        <v>299</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>1571</v>
+        <v>230</v>
       </c>
       <c r="H2" t="n">
-        <v>49.59</v>
+        <v>1.32</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1723000</v>
+        <v>58100</v>
       </c>
       <c r="K2" t="n">
-        <v>1722000</v>
+        <v>63200</v>
       </c>
       <c r="L2" t="n">
-        <v>1746000</v>
+        <v>63800</v>
       </c>
       <c r="M2" t="n">
-        <v>1722000</v>
+        <v>59000</v>
       </c>
       <c r="N2" t="n">
-        <v>49.71</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
-        <v>202799459000</v>
+        <v>20423419000</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>63800</v>
       </c>
       <c r="Q2" t="n">
-        <v>403000</v>
+        <v>25600</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>마이크론 급등 및 월가 발표에 따른 SK하이닉스 주가 상승 기대감. 솔리다임 중복 상장에 대한 비판 존재.</t>
+          <t>국내 시장 석권 준비 완료 및 폭등 전야 기대감 언급. 지분 경쟁 및 국산 위고비 판매 예정 등의 긍정적 요인 포함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['마이크론', '솔리다임', 'ADR']</t>
+          <t>['지분경쟁', '위고비', '바이오']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45850</v>
+        <v>1735000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-0.11%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>538</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="G3" t="n">
-        <v>320</v>
+        <v>1597</v>
       </c>
       <c r="H3" t="n">
-        <v>13.39</v>
+        <v>49.59</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>45900</v>
+        <v>1723000</v>
       </c>
       <c r="K3" t="n">
-        <v>45950</v>
+        <v>1722000</v>
       </c>
       <c r="L3" t="n">
-        <v>46150</v>
+        <v>1746000</v>
       </c>
       <c r="M3" t="n">
-        <v>45500</v>
+        <v>1722000</v>
       </c>
       <c r="N3" t="n">
-        <v>14.12</v>
+        <v>49.71</v>
       </c>
       <c r="O3" t="n">
-        <v>1265230750</v>
+        <v>460050779000</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>403000</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,20 +718,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB 주가 우상향 차트 분석 및 펩트론 기술 계약 해지에 따른 반사 이익 기대감.</t>
+          <t>마이크론 급등에 따른 SK하이닉스 반등 기대감 형성. 보호예수 물량 거래 및 솔리다임 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공매도', '전환사채', '우상향']</t>
+          <t>['마이크론', '반등', '보호예수']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,67 +740,67 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>221000</v>
+        <v>267750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-8.30%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.65</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>513</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>2339</v>
       </c>
       <c r="H4" t="n">
-        <v>3.47</v>
+        <v>46.38</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>241000</v>
+        <v>268500</v>
       </c>
       <c r="K4" t="n">
-        <v>227000</v>
+        <v>269500</v>
       </c>
       <c r="L4" t="n">
-        <v>230000</v>
+        <v>270000</v>
       </c>
       <c r="M4" t="n">
-        <v>221000</v>
+        <v>267000</v>
       </c>
       <c r="N4" t="n">
-        <v>4.12</v>
+        <v>46.37</v>
       </c>
       <c r="O4" t="n">
-        <v>2683746500</v>
+        <v>358014134250</v>
       </c>
       <c r="P4" t="n">
-        <v>1233000</v>
+        <v>374500</v>
       </c>
       <c r="Q4" t="n">
-        <v>120000</v>
+        <v>90200</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,29 +810,397 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>공매도 과열 지정 및 금지 조치에 따른 삼천당제약 주가 상승 기대감. 릴레이 계약 공시 및 미국 바이오주 강세 영향.</t>
+          <t>세계 최초 사기업 영업이익 107조 달성에도 불구하고 주가 부진에 대한 아쉬움 표출. 국장 전반의 저평가 및 희망 부재 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['영업이익', '저평가', '국장']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>45600</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-0.65%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="E5" t="n">
+        <v>82</v>
+      </c>
+      <c r="F5" t="n">
+        <v>48</v>
+      </c>
+      <c r="G5" t="n">
+        <v>346</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>45900</v>
+      </c>
+      <c r="K5" t="n">
+        <v>45950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>46150</v>
+      </c>
+      <c r="M5" t="n">
+        <v>45100</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3450291850</v>
+      </c>
+      <c r="P5" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>HLB 주가 우상향 차트 시작 기대감 및 펩트론 기술 계약 해지 관련 내용 언급. 공매도 및 전환사채 관계에 대한 논의.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['우상향', '공매도', '전환사채']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>16730</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-3.52%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E6" t="n">
+        <v>43</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>194</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>17340</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17190</v>
+      </c>
+      <c r="L6" t="n">
+        <v>17220</v>
+      </c>
+      <c r="M6" t="n">
+        <v>16720</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7893942065</v>
+      </c>
+      <c r="P6" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>대우건설 주주들에게 대차 해지의 중요성을 호소하며, 건설주 전반의 하락 추세에 대한 우려.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['대차해지', '호소', '하락']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>삼천당제약</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>224000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-7.05%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E7" t="n">
+        <v>68</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43</v>
+      </c>
+      <c r="G7" t="n">
+        <v>269</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>241000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>227000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>230000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>210500</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="O7" t="n">
+        <v>13239487500</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1233000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>공매도 과열 종목 지정 및 공매도 금지 예정 속에서, 릴레이 계약 공시 및 캐나다 세마 출시 기대감으로 인한 수급 쏠림 전망.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
         <v>0.5</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>['공매도', '계약공시', '바이오주']</t>
-        </is>
-      </c>
-      <c r="X4" t="n">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['공매도', '계약공시', '수급']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>2</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>000250</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9960</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-9.54%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E8" t="n">
+        <v>49</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" t="n">
+        <v>227</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9870</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2571861705</v>
+      </c>
+      <c r="P8" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>미국 항생제 회사 급등 및 케냐 에볼라 확진 소식 속 신풍제약 주가 변동에 대한 혼조세. 일부 긍정적 기대와 부정적 전망 혼재.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['항생제', '에볼라', '주가변동']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>019170</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261008_09.xlsx
+++ b/data/trending_integrated_20261008_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60500</v>
+        <v>59400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+4.13%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="H2" t="n">
         <v>1.32</v>
@@ -610,7 +610,7 @@
         <v>1.3</v>
       </c>
       <c r="O2" t="n">
-        <v>20423419000</v>
+        <v>24456920050</v>
       </c>
       <c r="P2" t="n">
         <v>63800</v>
@@ -619,23 +619,23 @@
         <v>25600</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-112000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국내 시장 석권 준비 완료 및 폭등 전야 기대감 언급. 지분 경쟁 및 국산 위고비 판매 예정 등의 긍정적 요인 포함.</t>
+          <t>국내 비만 치료제 시장 석권 기대감과 함께 신고가 돌파 후 변동성에 대한 분석. 공매도 현황 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['지분경쟁', '위고비', '바이오']</t>
+          <t>['비만 치료제', '신고가', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1735000</v>
+        <v>1739000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.93%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.12</v>
       </c>
       <c r="E3" t="n">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="F3" t="n">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="G3" t="n">
-        <v>1597</v>
+        <v>1648</v>
       </c>
       <c r="H3" t="n">
         <v>49.59</v>
@@ -702,7 +702,7 @@
         <v>49.71</v>
       </c>
       <c r="O3" t="n">
-        <v>460050779000</v>
+        <v>669207571000</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -711,7 +711,7 @@
         <v>403000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>267750</v>
+        <v>46150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'+0.54%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>-0.73</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
-        <v>513</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>2339</v>
+        <v>358</v>
       </c>
       <c r="H4" t="n">
-        <v>46.38</v>
+        <v>13.39</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>268500</v>
+        <v>45900</v>
       </c>
       <c r="K4" t="n">
-        <v>269500</v>
+        <v>45950</v>
       </c>
       <c r="L4" t="n">
-        <v>270000</v>
+        <v>46150</v>
       </c>
       <c r="M4" t="n">
-        <v>267000</v>
+        <v>45100</v>
       </c>
       <c r="N4" t="n">
-        <v>46.37</v>
+        <v>14.12</v>
       </c>
       <c r="O4" t="n">
-        <v>358014134250</v>
+        <v>4921020600</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>90200</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-13000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>세계 최초 사기업 영업이익 107조 달성에도 불구하고 주가 부진에 대한 아쉬움 표출. 국장 전반의 저평가 및 희망 부재 언급.</t>
+          <t>공매도와 전환사채 관계 분석. 우상향 차트와 펩트론 기술계약 해지 이슈로 인한 HLB의 반사이익 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['영업이익', '저평가', '국장']</t>
+          <t>['공매도', '전환사채', '반사이익']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45600</v>
+        <v>7830</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.65%</t>
+          <t>'+0.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.73</v>
+        <v>-2.03</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>346</v>
+        <v>138</v>
       </c>
       <c r="H5" t="n">
-        <v>13.39</v>
+        <v>3.09</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>45900</v>
+        <v>7820</v>
       </c>
       <c r="K5" t="n">
-        <v>45950</v>
+        <v>8080</v>
       </c>
       <c r="L5" t="n">
-        <v>46150</v>
+        <v>8510</v>
       </c>
       <c r="M5" t="n">
-        <v>45100</v>
+        <v>7580</v>
       </c>
       <c r="N5" t="n">
-        <v>14.12</v>
+        <v>5.12</v>
       </c>
       <c r="O5" t="n">
-        <v>3450291850</v>
+        <v>51527867615</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>23500</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>2890</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-377000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HLB 주가 우상향 차트 시작 기대감 및 펩트론 기술 계약 해지 관련 내용 언급. 공매도 및 전환사채 관계에 대한 논의.</t>
+          <t>3-4조 규모의 본PF 대주단 구성 중. 공매도 과열 관련 언급과 함께 대중과 반대로 매매해야 한다는 투자 전략 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우상향', '공매도', '전환사채']</t>
+          <t>['본PF', '공매도', '투자전략']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16730</v>
+        <v>268500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-3.52%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>528</v>
       </c>
       <c r="G6" t="n">
-        <v>194</v>
+        <v>2302</v>
       </c>
       <c r="H6" t="n">
-        <v>9.460000000000001</v>
+        <v>46.38</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17340</v>
+        <v>268500</v>
       </c>
       <c r="K6" t="n">
-        <v>17190</v>
+        <v>269500</v>
       </c>
       <c r="L6" t="n">
-        <v>17220</v>
+        <v>270000</v>
       </c>
       <c r="M6" t="n">
-        <v>16720</v>
+        <v>266500</v>
       </c>
       <c r="N6" t="n">
-        <v>9.5</v>
+        <v>46.37</v>
       </c>
       <c r="O6" t="n">
-        <v>7893942065</v>
+        <v>497199085750</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>90200</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-317000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설 주주들에게 대차 해지의 중요성을 호소하며, 건설주 전반의 하락 추세에 대한 우려.</t>
+          <t>107조 영업이익 달성에도 주가 하락. 대한민국 주식 시장의 낮은 평가와 정부 정책에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대차해지', '호소', '하락']</t>
+          <t>['영업이익', '저평가', '국장']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>224000</v>
+        <v>78300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-7.05%</t>
+          <t>'-2.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.65</v>
+        <v>-0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="H7" t="n">
-        <v>3.47</v>
+        <v>22.49</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>241000</v>
+        <v>80500</v>
       </c>
       <c r="K7" t="n">
-        <v>227000</v>
+        <v>79600</v>
       </c>
       <c r="L7" t="n">
-        <v>230000</v>
+        <v>79600</v>
       </c>
       <c r="M7" t="n">
-        <v>210500</v>
+        <v>77600</v>
       </c>
       <c r="N7" t="n">
-        <v>4.12</v>
+        <v>22.59</v>
       </c>
       <c r="O7" t="n">
-        <v>13239487500</v>
+        <v>28263336900</v>
       </c>
       <c r="P7" t="n">
-        <v>1233000</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>120000</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-47000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>공매도 과열 종목 지정 및 공매도 금지 예정 속에서, 릴레이 계약 공시 및 캐나다 세마 출시 기대감으로 인한 수급 쏠림 전망.</t>
+          <t>텍사스 가스 발전 수주에도 불구하고 주가 하락. 개인 투자자들의 매수세와 외국인의 매도 동향 주시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '계약공시', '수급']</t>
+          <t>['가스 발전', '수주', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9960</v>
+        <v>16940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-9.54%</t>
+          <t>'-4.78%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="H8" t="n">
-        <v>5.04</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,58 +1147,242 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11010</v>
+        <v>17790</v>
       </c>
       <c r="K8" t="n">
-        <v>10110</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10130</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>9870</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.01</v>
+        <v>9.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2571861705</v>
+        <v>10346000000</v>
       </c>
       <c r="P8" t="n">
-        <v>15900</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6310</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-11000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 항생제 회사 급등 및 케냐 에볼라 확진 소식 속 신풍제약 주가 변동에 대한 혼조세. 일부 긍정적 기대와 부정적 전망 혼재.</t>
+          <t>공매도 관련 우려와 대차 해지의 중요성을 강조하며 주주들에게 호소.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['공매도', '대차해지', '호소']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>삼천당제약</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>224500</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-6.85%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E9" t="n">
+        <v>75</v>
+      </c>
+      <c r="F9" t="n">
+        <v>45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>287</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>241000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>227000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>230000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>210500</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="O9" t="n">
+        <v>15763090750</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1233000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>120000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>공매도 과열 종목 지정 및 공매도 금지에도 불구하고 주가 하락. 릴레이 계약공시 기대감과 재료 소멸 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['공매도', '계약공시', '재료소멸']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>000250</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9920</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-9.90%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E10" t="n">
+        <v>59</v>
+      </c>
+      <c r="F10" t="n">
+        <v>46</v>
+      </c>
+      <c r="G10" t="n">
+        <v>240</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9870</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2984748070</v>
+      </c>
+      <c r="P10" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-256000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>케냐 에볼라 확진 소식과 함께 주가 급락. 일부 투자자들의 매도세와 향후 주가 전망에 대한 엇갈린 의견.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
         <v>0.2</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>['항생제', '에볼라', '주가변동']</t>
-        </is>
-      </c>
-      <c r="X8" t="n">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['에볼라', '주가급락', '매도세']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
         <v>2</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>019170</t>
         </is>

--- a/data/trending_integrated_20261008_09.xlsx
+++ b/data/trending_integrated_20261008_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59400</v>
+        <v>1741000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.24%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>619</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>351</v>
       </c>
       <c r="G2" t="n">
-        <v>246</v>
+        <v>1731</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
+        <v>49.59</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>58100</v>
+        <v>1723000</v>
       </c>
       <c r="K2" t="n">
-        <v>63200</v>
+        <v>1722000</v>
       </c>
       <c r="L2" t="n">
-        <v>63800</v>
+        <v>1750000</v>
       </c>
       <c r="M2" t="n">
-        <v>59000</v>
+        <v>1722000</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>49.71</v>
       </c>
       <c r="O2" t="n">
-        <v>24456920050</v>
+        <v>849943578000</v>
       </c>
       <c r="P2" t="n">
-        <v>63800</v>
+        <v>2987000</v>
       </c>
       <c r="Q2" t="n">
-        <v>25600</v>
+        <v>403000</v>
       </c>
       <c r="R2" t="n">
-        <v>-112000</v>
+        <v>21000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국내 비만 치료제 시장 석권 기대감과 함께 신고가 돌파 후 변동성에 대한 분석. 공매도 현황 언급.</t>
+          <t>마이크론 급등에 따른 SK하이닉스 반등 기대감 형성. 보호예수 물량 거래 및 솔리다임 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['비만 치료제', '신고가', '공매도']</t>
+          <t>['마이크론', '반등', '보호예수']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1739000</v>
+        <v>267500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.93%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>575</v>
+        <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>331</v>
+        <v>544</v>
       </c>
       <c r="G3" t="n">
-        <v>1648</v>
+        <v>2343</v>
       </c>
       <c r="H3" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1723000</v>
+        <v>268500</v>
       </c>
       <c r="K3" t="n">
-        <v>1722000</v>
+        <v>269500</v>
       </c>
       <c r="L3" t="n">
-        <v>1746000</v>
+        <v>270000</v>
       </c>
       <c r="M3" t="n">
-        <v>1722000</v>
+        <v>266500</v>
       </c>
       <c r="N3" t="n">
-        <v>49.71</v>
+        <v>46.37</v>
       </c>
       <c r="O3" t="n">
-        <v>669207571000</v>
+        <v>613216768500</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q3" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R3" t="n">
-        <v>21000</v>
+        <v>-317000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>마이크론 급등에 따른 SK하이닉스 반등 기대감 형성. 보호예수 물량 거래 및 솔리다임 관련 언급.</t>
+          <t>기록적인 3분기 영업이익에도 불구하고 주가 하락에 대한 불만 제기. 국내 증시 및 정치적 요인에 대한 비판.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크론', '반등', '보호예수']</t>
+          <t>['영업이익', '주가 하락', '국내 증시']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46150</v>
+        <v>7770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.54%</t>
+          <t>'-0.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.73</v>
+        <v>-2.03</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>358</v>
+        <v>169</v>
       </c>
       <c r="H4" t="n">
-        <v>13.39</v>
+        <v>3.09</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>45900</v>
+        <v>7820</v>
       </c>
       <c r="K4" t="n">
-        <v>45950</v>
+        <v>8080</v>
       </c>
       <c r="L4" t="n">
-        <v>46150</v>
+        <v>8510</v>
       </c>
       <c r="M4" t="n">
-        <v>45100</v>
+        <v>7580</v>
       </c>
       <c r="N4" t="n">
-        <v>14.12</v>
+        <v>5.12</v>
       </c>
       <c r="O4" t="n">
-        <v>4921020600</v>
+        <v>56860729555</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>23500</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>2890</v>
       </c>
       <c r="R4" t="n">
-        <v>-13000</v>
+        <v>-377000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>공매도와 전환사채 관계 분석. 우상향 차트와 펩트론 기술계약 해지 이슈로 인한 HLB의 반사이익 기대.</t>
+          <t>부동산 PF 사업 진행 및 대주단 구성 소식. 공매도 박멸 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공매도', '전환사채', '반사이익']</t>
+          <t>['부동산 PF', '대주단', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7830</v>
+        <v>45400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.13%</t>
+          <t>'-1.09%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.03</v>
+        <v>-0.73</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="H5" t="n">
-        <v>3.09</v>
+        <v>13.39</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7820</v>
+        <v>45900</v>
       </c>
       <c r="K5" t="n">
-        <v>8080</v>
+        <v>45950</v>
       </c>
       <c r="L5" t="n">
-        <v>8510</v>
+        <v>46150</v>
       </c>
       <c r="M5" t="n">
-        <v>7580</v>
+        <v>45100</v>
       </c>
       <c r="N5" t="n">
-        <v>5.12</v>
+        <v>14.12</v>
       </c>
       <c r="O5" t="n">
-        <v>51527867615</v>
+        <v>6464956400</v>
       </c>
       <c r="P5" t="n">
-        <v>23500</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>2890</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>-377000</v>
+        <v>-13000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3-4조 규모의 본PF 대주단 구성 중. 공매도 과열 관련 언급과 함께 대중과 반대로 매매해야 한다는 투자 전략 제시.</t>
+          <t>공매도와 전환사채 관계 분석. 우상향 차트와 펩트론 기술계약 해지 이슈로 인한 HLB의 반사이익 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['본PF', '공매도', '투자전략']</t>
+          <t>['공매도', '전환사채', '반사이익']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268500</v>
+        <v>57100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>131</v>
       </c>
       <c r="F6" t="n">
-        <v>528</v>
+        <v>78</v>
       </c>
       <c r="G6" t="n">
-        <v>2302</v>
+        <v>280</v>
       </c>
       <c r="H6" t="n">
-        <v>46.38</v>
+        <v>1.32</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>268500</v>
+        <v>58100</v>
       </c>
       <c r="K6" t="n">
-        <v>269500</v>
+        <v>63200</v>
       </c>
       <c r="L6" t="n">
-        <v>270000</v>
+        <v>63800</v>
       </c>
       <c r="M6" t="n">
-        <v>266500</v>
+        <v>56600</v>
       </c>
       <c r="N6" t="n">
-        <v>46.37</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
-        <v>497199085750</v>
+        <v>28337778550</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>63800</v>
       </c>
       <c r="Q6" t="n">
-        <v>90200</v>
+        <v>25600</v>
       </c>
       <c r="R6" t="n">
-        <v>-317000</v>
+        <v>-112000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>107조 영업이익 달성에도 주가 하락. 대한민국 주식 시장의 낮은 평가와 정부 정책에 대한 불만 표출.</t>
+          <t>국내 비만 치료제 시장 석권 기대감. 유통 물량 적음 및 미국 비만주 급등에 따른 긍정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['영업이익', '저평가', '국장']</t>
+          <t>['비만 치료제', '시장 석권', '유통 물량']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78300</v>
+        <v>19120</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.73%</t>
+          <t>'-2.15%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>281</v>
+        <v>102</v>
       </c>
       <c r="H7" t="n">
-        <v>22.49</v>
+        <v>27.68</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>80500</v>
+        <v>19540</v>
       </c>
       <c r="K7" t="n">
-        <v>79600</v>
+        <v>19490</v>
       </c>
       <c r="L7" t="n">
-        <v>79600</v>
+        <v>19500</v>
       </c>
       <c r="M7" t="n">
-        <v>77600</v>
+        <v>19110</v>
       </c>
       <c r="N7" t="n">
-        <v>22.59</v>
+        <v>27.67</v>
       </c>
       <c r="O7" t="n">
-        <v>28263336900</v>
+        <v>11056603680</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>18440</v>
       </c>
       <c r="R7" t="n">
-        <v>-47000</v>
+        <v>-56000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>텍사스 가스 발전 수주에도 불구하고 주가 하락. 개인 투자자들의 매수세와 외국인의 매도 동향 주시.</t>
+          <t>조선업 수주 상황 악화 및 경쟁 심화에 대한 부정적 전망. 증권사 분석 및 개미 투자자에 대한 불신.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['가스 발전', '수주', '외국인']</t>
+          <t>['수주 부진', '조선업', '애널리스트 비판']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16940</v>
+        <v>16790</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-4.78%</t>
+          <t>'-3.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="H8" t="n">
         <v>9.460000000000001</v>
@@ -1147,28 +1147,28 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17790</v>
+        <v>17340</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>17190</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>17220</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>16710</v>
       </c>
       <c r="N8" t="n">
         <v>9.5</v>
       </c>
       <c r="O8" t="n">
-        <v>10346000000</v>
+        <v>12258180085</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
         <v>-11000</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>공매도 관련 우려와 대차 해지의 중요성을 강조하며 주주들에게 호소.</t>
+          <t>대차 해지를 통한 주가 부양 호소. 공매도 과열 종목 지정 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '호소']</t>
+          <t>['대차 해지', '공매도', '주주 호소']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,79 +1207,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>224500</v>
+        <v>77900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-6.85%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.65</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>287</v>
+        <v>342</v>
       </c>
       <c r="H9" t="n">
-        <v>3.47</v>
+        <v>22.49</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>241000</v>
+        <v>80500</v>
       </c>
       <c r="K9" t="n">
-        <v>227000</v>
+        <v>79600</v>
       </c>
       <c r="L9" t="n">
-        <v>230000</v>
+        <v>79600</v>
       </c>
       <c r="M9" t="n">
-        <v>210500</v>
+        <v>77600</v>
       </c>
       <c r="N9" t="n">
-        <v>4.12</v>
+        <v>22.59</v>
       </c>
       <c r="O9" t="n">
-        <v>15763090750</v>
+        <v>38628097900</v>
       </c>
       <c r="P9" t="n">
-        <v>1233000</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>120000</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>12000</v>
+        <v>-47000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>공매도 과열 종목 지정 및 공매도 금지에도 불구하고 주가 하락. 릴레이 계약공시 기대감과 재료 소멸 가능성 언급.</t>
+          <t>해외 가스 발전 수주 소식에도 불구하고 주가 하락에 대한 실망감 표현. 개인 투자자들의 쏠림 현상 및 공매도에 대한 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '계약공시', '재료소멸']</t>
+          <t>['가스 발전', '주가 하락', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9920</v>
+        <v>228000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-9.90%</t>
+          <t>'-5.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.03</v>
+        <v>-0.65</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>240</v>
+        <v>317</v>
       </c>
       <c r="H10" t="n">
-        <v>5.04</v>
+        <v>3.47</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11010</v>
+        <v>241000</v>
       </c>
       <c r="K10" t="n">
-        <v>10110</v>
+        <v>227000</v>
       </c>
       <c r="L10" t="n">
-        <v>10130</v>
+        <v>230000</v>
       </c>
       <c r="M10" t="n">
-        <v>9870</v>
+        <v>210500</v>
       </c>
       <c r="N10" t="n">
-        <v>5.01</v>
+        <v>4.12</v>
       </c>
       <c r="O10" t="n">
-        <v>2984748070</v>
+        <v>17824056250</v>
       </c>
       <c r="P10" t="n">
-        <v>15900</v>
+        <v>1233000</v>
       </c>
       <c r="Q10" t="n">
-        <v>6310</v>
+        <v>120000</v>
       </c>
       <c r="R10" t="n">
-        <v>-256000</v>
+        <v>12000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>케냐 에볼라 확진 소식과 함께 주가 급락. 일부 투자자들의 매도세와 향후 주가 전망에 대한 엇갈린 의견.</t>
+          <t>캐나다 세마 위탁 생산 및 릴레이 계약 공시 기대감. 공매도 금지 조치와 더불어 수급 긍정 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['에볼라', '주가급락', '매도세']</t>
+          <t>['위탁 생산', '계약 공시', '공매도 금지']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1383,6 +1383,190 @@
         </is>
       </c>
       <c r="Z10" t="inlineStr">
+        <is>
+          <t>000250</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4815</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-7.58%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>52</v>
+      </c>
+      <c r="F11" t="n">
+        <v>37</v>
+      </c>
+      <c r="G11" t="n">
+        <v>130</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>5210</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5220</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5310</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4755</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="O11" t="n">
+        <v>30089971304</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>592</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-150000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>전환사채 발행으로 인한 대규모 물량 출회 우려. 주가 급락 가능성 및 악재 발생에 대한 부정적 전망.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['전환사채', '주가 급락', '악재']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-9.17%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E12" t="n">
+        <v>62</v>
+      </c>
+      <c r="F12" t="n">
+        <v>48</v>
+      </c>
+      <c r="G12" t="n">
+        <v>251</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9870</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3288988935</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-256000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>미국 항생제 회사 주가 급등 소식과 대조되는 주가 흐름. 잦은 주가 조작 및 털기 의혹 제기.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['항생제', '주가 조작', '털기']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>019170</t>
         </is>

--- a/data/trending_integrated_20261008_09.xlsx
+++ b/data/trending_integrated_20261008_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1741000</v>
+        <v>4590</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+1.04%</t>
+          <t>'+3.61%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.12</v>
+        <v>1.19</v>
       </c>
       <c r="E2" t="n">
-        <v>619</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>351</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>1731</v>
+        <v>76</v>
       </c>
       <c r="H2" t="n">
-        <v>49.59</v>
+        <v>4.46</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1723000</v>
+        <v>4430</v>
       </c>
       <c r="K2" t="n">
-        <v>1722000</v>
+        <v>4650</v>
       </c>
       <c r="L2" t="n">
-        <v>1750000</v>
+        <v>4855</v>
       </c>
       <c r="M2" t="n">
-        <v>1722000</v>
+        <v>4255</v>
       </c>
       <c r="N2" t="n">
-        <v>49.71</v>
+        <v>3.27</v>
       </c>
       <c r="O2" t="n">
-        <v>849943578000</v>
+        <v>44933733986</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>5470</v>
       </c>
       <c r="Q2" t="n">
-        <v>403000</v>
+        <v>2810</v>
       </c>
       <c r="R2" t="n">
-        <v>21000</v>
+        <v>-22000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>마이크론 급등에 따른 SK하이닉스 반등 기대감 형성. 보호예수 물량 거래 및 솔리다임 관련 언급.</t>
+          <t>전염병 관련 전세계 약 필요성 언급, 5000원 돌파 시 매도 의견 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['마이크론', '반등', '보호예수']</t>
+          <t>['전염병', '항생제', '신풍제약']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>267500</v>
+        <v>1728000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'+0.29%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>654</v>
       </c>
       <c r="F3" t="n">
-        <v>544</v>
+        <v>370</v>
       </c>
       <c r="G3" t="n">
-        <v>2343</v>
+        <v>1772</v>
       </c>
       <c r="H3" t="n">
-        <v>46.38</v>
+        <v>49.59</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>268500</v>
+        <v>1723000</v>
       </c>
       <c r="K3" t="n">
-        <v>269500</v>
+        <v>1722000</v>
       </c>
       <c r="L3" t="n">
-        <v>270000</v>
+        <v>1750000</v>
       </c>
       <c r="M3" t="n">
-        <v>266500</v>
+        <v>1722000</v>
       </c>
       <c r="N3" t="n">
-        <v>46.37</v>
+        <v>49.71</v>
       </c>
       <c r="O3" t="n">
-        <v>613216768500</v>
+        <v>964599186500</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q3" t="n">
-        <v>90200</v>
+        <v>403000</v>
       </c>
       <c r="R3" t="n">
-        <v>-317000</v>
+        <v>21000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>기록적인 3분기 영업이익에도 불구하고 주가 하락에 대한 불만 제기. 국내 증시 및 정치적 요인에 대한 비판.</t>
+          <t>마이크론 급등에 따른 SK하이닉스 반등 기대감 형성. 보호예수 물량 거래 및 솔리다임 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '국내 증시']</t>
+          <t>['마이크론', '반등', '보호예수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7770</v>
+        <v>267000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.64%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.03</v>
+        <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>551</v>
       </c>
       <c r="G4" t="n">
-        <v>169</v>
+        <v>2381</v>
       </c>
       <c r="H4" t="n">
-        <v>3.09</v>
+        <v>46.38</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7820</v>
+        <v>268500</v>
       </c>
       <c r="K4" t="n">
-        <v>8080</v>
+        <v>269500</v>
       </c>
       <c r="L4" t="n">
-        <v>8510</v>
+        <v>270000</v>
       </c>
       <c r="M4" t="n">
-        <v>7580</v>
+        <v>266000</v>
       </c>
       <c r="N4" t="n">
-        <v>5.12</v>
+        <v>46.37</v>
       </c>
       <c r="O4" t="n">
-        <v>56860729555</v>
+        <v>764841796000</v>
       </c>
       <c r="P4" t="n">
-        <v>23500</v>
+        <v>374500</v>
       </c>
       <c r="Q4" t="n">
-        <v>2890</v>
+        <v>90200</v>
       </c>
       <c r="R4" t="n">
-        <v>-377000</v>
+        <v>-317000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>부동산 PF 사업 진행 및 대주단 구성 소식. 공매도 박멸 및 주가 상승 기대.</t>
+          <t>역대급 실적에도 하락하는 증시에 대한 불만과 정치권 책임론 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['부동산 PF', '대주단', '공매도']</t>
+          <t>['영업이익', '실적', '국장']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45400</v>
+        <v>7770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.09%</t>
+          <t>'-0.64%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.73</v>
+        <v>-2.03</v>
       </c>
       <c r="E5" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>384</v>
+        <v>211</v>
       </c>
       <c r="H5" t="n">
-        <v>13.39</v>
+        <v>3.09</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>45900</v>
+        <v>7820</v>
       </c>
       <c r="K5" t="n">
-        <v>45950</v>
+        <v>8080</v>
       </c>
       <c r="L5" t="n">
-        <v>46150</v>
+        <v>8510</v>
       </c>
       <c r="M5" t="n">
-        <v>45100</v>
+        <v>7580</v>
       </c>
       <c r="N5" t="n">
-        <v>14.12</v>
+        <v>5.12</v>
       </c>
       <c r="O5" t="n">
-        <v>6464956400</v>
+        <v>58078387255</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>23500</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>2890</v>
       </c>
       <c r="R5" t="n">
-        <v>-13000</v>
+        <v>-377000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>공매도와 전환사채 관계 분석. 우상향 차트와 펩트론 기술계약 해지 이슈로 인한 HLB의 반사이익 기대.</t>
+          <t>본 PF 및 대주단 구성 진행 상황 언급, 공매도 박멸 및 물량 간수 독려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공매도', '전환사채', '반사이익']</t>
+          <t>['본PF', '공매도', '대주단']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57100</v>
+        <v>45300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.02</v>
+        <v>-0.73</v>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>280</v>
+        <v>398</v>
       </c>
       <c r="H6" t="n">
-        <v>1.32</v>
+        <v>13.39</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>58100</v>
+        <v>45900</v>
       </c>
       <c r="K6" t="n">
-        <v>63200</v>
+        <v>45950</v>
       </c>
       <c r="L6" t="n">
-        <v>63800</v>
+        <v>46150</v>
       </c>
       <c r="M6" t="n">
-        <v>56600</v>
+        <v>45100</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>14.12</v>
       </c>
       <c r="O6" t="n">
-        <v>28337778550</v>
+        <v>7296655125</v>
       </c>
       <c r="P6" t="n">
-        <v>63800</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>25600</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-112000</v>
+        <v>-13000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>국내 비만 치료제 시장 석권 기대감. 유통 물량 적음 및 미국 비만주 급등에 따른 긍정적 전망.</t>
+          <t>담관암 신약 기대감 및 펩트론 계약 해지로 인한 반사이익 전망, 우상향 차트 분석.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['비만 치료제', '시장 석권', '유통 물량']</t>
+          <t>['담관암', '신약', '우상향']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19120</v>
+        <v>19200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H7" t="n">
         <v>27.68</v>
@@ -1070,7 +1070,7 @@
         <v>27.67</v>
       </c>
       <c r="O7" t="n">
-        <v>11056603680</v>
+        <v>12479904475</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>조선업 수주 상황 악화 및 경쟁 심화에 대한 부정적 전망. 증권사 분석 및 개미 투자자에 대한 불신.</t>
+          <t>조선업 수주 부진 및 경쟁 심화 언급, 개미 투자자 손실 가능성 경고.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주 부진', '조선업', '애널리스트 비판']</t>
+          <t>['수주', '조선주', '신저점']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16790</v>
+        <v>16950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.17%</t>
+          <t>'-2.25%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="H8" t="n">
         <v>9.460000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.5</v>
       </c>
       <c r="O8" t="n">
-        <v>12258180085</v>
+        <v>13793902960</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대차 해지를 통한 주가 부양 호소. 공매도 과열 종목 지정 가능성 언급.</t>
+          <t>공매도 및 대차 관련 우려 제기, 주주들에게 대차 해지의 중요성 강조.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '주주 호소']</t>
+          <t>['공매도', '대차', '대우건설']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77900</v>
+        <v>78000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.23%</t>
+          <t>'-3.11%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="G9" t="n">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="H9" t="n">
         <v>22.49</v>
@@ -1254,7 +1254,7 @@
         <v>22.59</v>
       </c>
       <c r="O9" t="n">
-        <v>38628097900</v>
+        <v>41505981550</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>해외 가스 발전 수주 소식에도 불구하고 주가 하락에 대한 실망감 표현. 개인 투자자들의 쏠림 현상 및 공매도에 대한 우려.</t>
+          <t>미국 가스 발전 수주 확정 및 원전 관련 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['가스 발전', '주가 하락', '공매도']</t>
+          <t>['원전', '수출', '가스발전']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>228000</v>
+        <v>232500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-5.39%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.65</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="H10" t="n">
         <v>3.47</v>
@@ -1337,7 +1337,7 @@
         <v>227000</v>
       </c>
       <c r="L10" t="n">
-        <v>230000</v>
+        <v>233000</v>
       </c>
       <c r="M10" t="n">
         <v>210500</v>
@@ -1346,7 +1346,7 @@
         <v>4.12</v>
       </c>
       <c r="O10" t="n">
-        <v>17824056250</v>
+        <v>19621439500</v>
       </c>
       <c r="P10" t="n">
         <v>1233000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>캐나다 세마 위탁 생산 및 릴레이 계약 공시 기대감. 공매도 금지 조치와 더불어 수급 긍정 전망.</t>
+          <t>공매도 과열 종목 지정 및 릴레이 계약 공시 내용 언급, 주가 하락 가능성 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['위탁 생산', '계약 공시', '공매도 금지']</t>
+          <t>['공매도', '계약공시', '주가하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4815</v>
+        <v>17150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-7.58%</t>
+          <t>'-4.40%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.95</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="H11" t="n">
-        <v>4.65</v>
+        <v>3.97</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5210</v>
+        <v>17940</v>
       </c>
       <c r="K11" t="n">
-        <v>5220</v>
+        <v>17770</v>
       </c>
       <c r="L11" t="n">
-        <v>5310</v>
+        <v>17940</v>
       </c>
       <c r="M11" t="n">
-        <v>4755</v>
+        <v>16930</v>
       </c>
       <c r="N11" t="n">
-        <v>4.72</v>
+        <v>4.92</v>
       </c>
       <c r="O11" t="n">
-        <v>30089971304</v>
+        <v>36732206170</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-150000</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>전환사채 발행으로 인한 대규모 물량 출회 우려. 주가 급락 가능성 및 악재 발생에 대한 부정적 전망.</t>
+          <t>미국 광통신주 하락세 언급, 적자 기업에 대한 투자 경계 및 주가 하락 예상.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['전환사채', '주가 급락', '악재']</t>
+          <t>['광통신', '적자기업', '하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10000</v>
+        <v>54900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-9.17%</t>
+          <t>'-5.51%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
-        <v>251</v>
+        <v>309</v>
       </c>
       <c r="H12" t="n">
-        <v>5.04</v>
+        <v>1.32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,58 +1515,242 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11010</v>
+        <v>58100</v>
       </c>
       <c r="K12" t="n">
-        <v>10110</v>
+        <v>63200</v>
       </c>
       <c r="L12" t="n">
-        <v>10130</v>
+        <v>63800</v>
       </c>
       <c r="M12" t="n">
-        <v>9870</v>
+        <v>54900</v>
       </c>
       <c r="N12" t="n">
-        <v>5.01</v>
+        <v>1.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3288988935</v>
+        <v>31691694450</v>
       </c>
       <c r="P12" t="n">
-        <v>15900</v>
+        <v>63800</v>
       </c>
       <c r="Q12" t="n">
-        <v>6310</v>
+        <v>25600</v>
       </c>
       <c r="R12" t="n">
-        <v>-256000</v>
+        <v>-112000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 항생제 회사 주가 급등 소식과 대조되는 주가 흐름. 잦은 주가 조작 및 털기 의혹 제기.</t>
+          <t>미국 비만주 급등과 국내 시장 관련 언급. 불법 조작 거래 및 신고 관련 주장.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['비만약', '주가 조작', '거래량']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>008930</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4845</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-7.01%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42</v>
+      </c>
+      <c r="G13" t="n">
+        <v>153</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5210</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5220</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5310</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4755</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="O13" t="n">
+        <v>34305694654</v>
+      </c>
+      <c r="P13" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>592</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-150000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>전환사채 발행 및 대규모 장내매도 악재 발생, 주가 하락 우려.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
         <v>0.2</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>['항생제', '주가 조작', '털기']</t>
-        </is>
-      </c>
-      <c r="X12" t="n">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['전환사채', '악재', '장내매도']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10010</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-9.08%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E14" t="n">
+        <v>63</v>
+      </c>
+      <c r="F14" t="n">
+        <v>47</v>
+      </c>
+      <c r="G14" t="n">
+        <v>255</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9870</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3465298520</v>
+      </c>
+      <c r="P14" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-256000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>미국 항생제 회사 주가 급등 언급. 케냐 에볼라, 러시아 관련 부정적 언급.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['항생제', '에볼라', '주가 급등']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>019170</t>
         </is>

--- a/data/trending_integrated_20261008_09.xlsx
+++ b/data/trending_integrated_20261008_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4590</v>
+        <v>7200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+3.61%</t>
+          <t>'+11.46%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.19</v>
+        <v>-0.31</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H2" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4430</v>
+        <v>6460</v>
       </c>
       <c r="K2" t="n">
-        <v>4650</v>
+        <v>6930</v>
       </c>
       <c r="L2" t="n">
-        <v>4855</v>
+        <v>8390</v>
       </c>
       <c r="M2" t="n">
-        <v>4255</v>
+        <v>6910</v>
       </c>
       <c r="N2" t="n">
-        <v>3.27</v>
+        <v>0.31</v>
       </c>
       <c r="O2" t="n">
-        <v>44933733986</v>
+        <v>15574461320</v>
       </c>
       <c r="P2" t="n">
-        <v>5470</v>
+        <v>9680</v>
       </c>
       <c r="Q2" t="n">
-        <v>2810</v>
+        <v>371</v>
       </c>
       <c r="R2" t="n">
-        <v>-22000</v>
+        <v>-23000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>전염병 관련 전세계 약 필요성 언급, 5000원 돌파 시 매도 의견 제시.</t>
+          <t>신규 주주 확정 및 투자금 유입 소식이 있으나, 재료 소멸에 대한 우려와 함께 일부 투자자는 매도를 고려하고 있음. 긍정적 전망과 경계가 공존.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['전염병', '항생제', '신풍제약']</t>
+          <t>['신규 투자', '재료 소멸', '유통 물량']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1728000</v>
+        <v>4700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.29%</t>
+          <t>'+6.09%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.12</v>
+        <v>1.19</v>
       </c>
       <c r="E3" t="n">
-        <v>654</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>370</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>1772</v>
+        <v>111</v>
       </c>
       <c r="H3" t="n">
-        <v>49.59</v>
+        <v>4.46</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1723000</v>
+        <v>4430</v>
       </c>
       <c r="K3" t="n">
-        <v>1722000</v>
+        <v>4650</v>
       </c>
       <c r="L3" t="n">
-        <v>1750000</v>
+        <v>4855</v>
       </c>
       <c r="M3" t="n">
-        <v>1722000</v>
+        <v>4255</v>
       </c>
       <c r="N3" t="n">
-        <v>49.71</v>
+        <v>3.27</v>
       </c>
       <c r="O3" t="n">
-        <v>964599186500</v>
+        <v>50208780318</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>5470</v>
       </c>
       <c r="Q3" t="n">
-        <v>403000</v>
+        <v>2810</v>
       </c>
       <c r="R3" t="n">
-        <v>21000</v>
+        <v>-470000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>마이크론 급등에 따른 SK하이닉스 반등 기대감 형성. 보호예수 물량 거래 및 솔리다임 관련 언급.</t>
+          <t>전염병 관련 소식과 미국 항생제 회사 주가 급등 소식을 언급하며, 일부는 투자 기회로 해석하는 분위기. 다만, 검증 가능한 근거는 부족함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크론', '반등', '보호예수']</t>
+          <t>['전염병', '항생제', '주가 급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>267000</v>
+        <v>1736000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>693</v>
       </c>
       <c r="F4" t="n">
-        <v>551</v>
+        <v>394</v>
       </c>
       <c r="G4" t="n">
-        <v>2381</v>
+        <v>1829</v>
       </c>
       <c r="H4" t="n">
-        <v>46.38</v>
+        <v>49.59</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>268500</v>
+        <v>1723000</v>
       </c>
       <c r="K4" t="n">
-        <v>269500</v>
+        <v>1722000</v>
       </c>
       <c r="L4" t="n">
-        <v>270000</v>
+        <v>1750000</v>
       </c>
       <c r="M4" t="n">
-        <v>266000</v>
+        <v>1722000</v>
       </c>
       <c r="N4" t="n">
-        <v>46.37</v>
+        <v>49.71</v>
       </c>
       <c r="O4" t="n">
-        <v>764841796000</v>
+        <v>1063894146000</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>90200</v>
+        <v>403000</v>
       </c>
       <c r="R4" t="n">
-        <v>-317000</v>
+        <v>-21000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>역대급 실적에도 하락하는 증시에 대한 불만과 정치권 책임론 제기.</t>
+          <t>마이크론 급등에 따른 SK하이닉스 반등 기대감 형성. 보호예수 물량 거래 및 솔리다임 관련 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['영업이익', '실적', '국장']</t>
+          <t>['마이크론', '반등', '보호예수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7770</v>
+        <v>45800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.64%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.03</v>
+        <v>-0.73</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>211</v>
+        <v>426</v>
       </c>
       <c r="H5" t="n">
-        <v>3.09</v>
+        <v>13.39</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7820</v>
+        <v>45900</v>
       </c>
       <c r="K5" t="n">
-        <v>8080</v>
+        <v>45950</v>
       </c>
       <c r="L5" t="n">
-        <v>8510</v>
+        <v>46150</v>
       </c>
       <c r="M5" t="n">
-        <v>7580</v>
+        <v>45100</v>
       </c>
       <c r="N5" t="n">
-        <v>5.12</v>
+        <v>14.12</v>
       </c>
       <c r="O5" t="n">
-        <v>58078387255</v>
+        <v>8046697250</v>
       </c>
       <c r="P5" t="n">
-        <v>23500</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>2890</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>-377000</v>
+        <v>-14000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>본 PF 및 대주단 구성 진행 상황 언급, 공매도 박멸 및 물량 간수 독려.</t>
+          <t>간암 치료제 허가 관련 긍정적인 뉴스와 함께 공매도 세력에 대한 언급이 있으며, 우상향 추세에 대한 기대감이 나타남. 공시 기반 팩트와 기대감 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['본PF', '공매도', '대주단']</t>
+          <t>['간암 치료제', '공매도', '우상향 추세']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45300</v>
+        <v>267000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.73</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>556</v>
       </c>
       <c r="G6" t="n">
-        <v>398</v>
+        <v>2346</v>
       </c>
       <c r="H6" t="n">
-        <v>13.39</v>
+        <v>46.38</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>45900</v>
+        <v>268500</v>
       </c>
       <c r="K6" t="n">
-        <v>45950</v>
+        <v>269500</v>
       </c>
       <c r="L6" t="n">
-        <v>46150</v>
+        <v>270000</v>
       </c>
       <c r="M6" t="n">
-        <v>45100</v>
+        <v>266000</v>
       </c>
       <c r="N6" t="n">
-        <v>14.12</v>
+        <v>46.37</v>
       </c>
       <c r="O6" t="n">
-        <v>7296655125</v>
+        <v>867325343750</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>90200</v>
       </c>
       <c r="R6" t="n">
-        <v>-13000</v>
+        <v>-246000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-228000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>담관암 신약 기대감 및 펩트론 계약 해지로 인한 반사이익 전망, 우상향 차트 분석.</t>
+          <t>역대급 영업이익에도 불구하고 주가가 하락하는 현실에 대한 불만과 정부 및 증시 시스템에 대한 비판이 주를 이룸. 실적이라는 팩트 기반 비판.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['담관암', '신약', '우상향']</t>
+          <t>['영업이익', '주가 하락', '증시 비판']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19200</v>
+        <v>19185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-1.82%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H7" t="n">
         <v>27.68</v>
@@ -1070,7 +1070,7 @@
         <v>27.67</v>
       </c>
       <c r="O7" t="n">
-        <v>12479904475</v>
+        <v>13384629725</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1079,14 +1079,14 @@
         <v>18440</v>
       </c>
       <c r="R7" t="n">
-        <v>-56000</v>
+        <v>-75000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>조선업 수주 부진 및 경쟁 심화 언급, 개미 투자자 손실 가능성 경고.</t>
+          <t>조선주 전반의 부진에 대한 언급과 함께, 수주 소식에도 불구하고 주가 하락을 예상하는 부정적인 전망이 지배적. 팩트 기반 분석은 미흡.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '조선주', '신저점']</t>
+          <t>['조선주', '주가 하락', '수주 부진']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16950</v>
+        <v>7670</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.25%</t>
+          <t>'-1.92%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>-2.03</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="H8" t="n">
-        <v>9.460000000000001</v>
+        <v>3.09</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17340</v>
+        <v>7820</v>
       </c>
       <c r="K8" t="n">
-        <v>17190</v>
+        <v>8080</v>
       </c>
       <c r="L8" t="n">
-        <v>17220</v>
+        <v>8510</v>
       </c>
       <c r="M8" t="n">
-        <v>16710</v>
+        <v>7550</v>
       </c>
       <c r="N8" t="n">
-        <v>9.5</v>
+        <v>5.12</v>
       </c>
       <c r="O8" t="n">
-        <v>13793902960</v>
+        <v>61945021115</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>23500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>2890</v>
       </c>
       <c r="R8" t="n">
-        <v>-11000</v>
+        <v>-496000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>공매도 및 대차 관련 우려 제기, 주주들에게 대차 해지의 중요성 강조.</t>
+          <t>건설 및 부동산 관련 내용과 함께 일부 투자자 간의 논쟁이 나타나지만, 종목의 명확한 팩트나 전망에 대한 분석은 부족함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '대우건설']</t>
+          <t>['부동산', '건설', '투자자 논쟁']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78000</v>
+        <v>16895</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.11%</t>
+          <t>'-2.57%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>359</v>
+        <v>262</v>
       </c>
       <c r="H9" t="n">
-        <v>22.49</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>80500</v>
+        <v>17340</v>
       </c>
       <c r="K9" t="n">
-        <v>79600</v>
+        <v>17190</v>
       </c>
       <c r="L9" t="n">
-        <v>79600</v>
+        <v>17220</v>
       </c>
       <c r="M9" t="n">
-        <v>77600</v>
+        <v>16710</v>
       </c>
       <c r="N9" t="n">
-        <v>22.59</v>
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
-        <v>41505981550</v>
+        <v>15601691760</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-47000</v>
+        <v>35000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 가스 발전 수주 확정 및 원전 관련 긍정적 전망 제시.</t>
+          <t>공매도와 대차해지에 대한 우려와 호소가 반복적으로 나타나지만, 구체적인 팩트나 분석 내용은 부족함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '수출', '가스발전']</t>
+          <t>['공매도', '대차해지', '주주 호소']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>232500</v>
+        <v>234500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-2.70%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.65</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="H10" t="n">
         <v>3.47</v>
@@ -1337,7 +1337,7 @@
         <v>227000</v>
       </c>
       <c r="L10" t="n">
-        <v>233000</v>
+        <v>235000</v>
       </c>
       <c r="M10" t="n">
         <v>210500</v>
@@ -1346,7 +1346,7 @@
         <v>4.12</v>
       </c>
       <c r="O10" t="n">
-        <v>19621439500</v>
+        <v>21965591250</v>
       </c>
       <c r="P10" t="n">
         <v>1233000</v>
@@ -1355,14 +1355,14 @@
         <v>120000</v>
       </c>
       <c r="R10" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 과열 종목 지정 및 릴레이 계약 공시 내용 언급, 주가 하락 가능성 제시.</t>
+          <t>공매도 과열 종목 지정 가능성 언급 및 릴레이 계약 공시 기대감. 해외 바이오주 상승에 따른 수급 몰림 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '계약공시', '주가하락']</t>
+          <t>['공매도', '계약 공시', '바이오']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17150</v>
+        <v>77100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.40%</t>
+          <t>'-4.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.95</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="G11" t="n">
-        <v>197</v>
+        <v>404</v>
       </c>
       <c r="H11" t="n">
-        <v>3.97</v>
+        <v>22.49</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17940</v>
+        <v>80500</v>
       </c>
       <c r="K11" t="n">
-        <v>17770</v>
+        <v>79600</v>
       </c>
       <c r="L11" t="n">
-        <v>17940</v>
+        <v>79600</v>
       </c>
       <c r="M11" t="n">
-        <v>16930</v>
+        <v>77000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.92</v>
+        <v>22.59</v>
       </c>
       <c r="O11" t="n">
-        <v>36732206170</v>
+        <v>55443102850</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-83000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-40000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락세 언급, 적자 기업에 대한 투자 경계 및 주가 하락 예상.</t>
+          <t>해외 가스 발전 수주 및 원전 관련 소식이 있으나, 주가 하락에 대한 불만과 공매도에 대한 우려가 더 큰 비중을 차지. 팩트보다 감정적 반응이 많음.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '적자기업', '하락']</t>
+          <t>['가스 발전', '원전', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54900</v>
+        <v>17090</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.51%</t>
+          <t>'-4.74%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>-0.95</v>
       </c>
       <c r="E12" t="n">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>309</v>
+        <v>217</v>
       </c>
       <c r="H12" t="n">
-        <v>1.32</v>
+        <v>3.97</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>58100</v>
+        <v>17940</v>
       </c>
       <c r="K12" t="n">
-        <v>63200</v>
+        <v>17770</v>
       </c>
       <c r="L12" t="n">
-        <v>63800</v>
+        <v>17940</v>
       </c>
       <c r="M12" t="n">
-        <v>54900</v>
+        <v>16930</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3</v>
+        <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>31691694450</v>
+        <v>40803537295</v>
       </c>
       <c r="P12" t="n">
-        <v>63800</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>25600</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-112000</v>
+        <v>15000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 비만주 급등과 국내 시장 관련 언급. 불법 조작 거래 및 신고 관련 주장.</t>
+          <t>미국 광통신주의 하락세와 함께 국내 종목의 주가 하락 및 적자 기업에 대한 부정적인 시각이 주를 이룸. 팩트 기반 전망보다는 부정적 감정이 강함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['비만약', '주가 조작', '거래량']</t>
+          <t>['광통신', '주가 하락', '적자 기업']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4845</v>
+        <v>54800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-7.01%</t>
+          <t>'-5.68%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>175</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="G13" t="n">
-        <v>153</v>
+        <v>339</v>
       </c>
       <c r="H13" t="n">
-        <v>4.65</v>
+        <v>1.32</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5210</v>
+        <v>58100</v>
       </c>
       <c r="K13" t="n">
-        <v>5220</v>
+        <v>63200</v>
       </c>
       <c r="L13" t="n">
-        <v>5310</v>
+        <v>63800</v>
       </c>
       <c r="M13" t="n">
-        <v>4755</v>
+        <v>54400</v>
       </c>
       <c r="N13" t="n">
-        <v>4.72</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="n">
-        <v>34305694654</v>
+        <v>34917414100</v>
       </c>
       <c r="P13" t="n">
-        <v>8100</v>
+        <v>63800</v>
       </c>
       <c r="Q13" t="n">
-        <v>592</v>
+        <v>25600</v>
       </c>
       <c r="R13" t="n">
-        <v>-150000</v>
+        <v>-154000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 대규모 장내매도 악재 발생, 주가 하락 우려.</t>
+          <t>국내 최초 비만약 관련 기대감과 함께 주가 하락 및 조작 의혹 제기. 투자자들의 불만 고조.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['전환사채', '악재', '장내매도']</t>
+          <t>['비만약', '조작 거래', '하한가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,97 +1660,189 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10010</v>
+        <v>4825</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-9.08%</t>
+          <t>'-7.39%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>176</v>
       </c>
       <c r="H14" t="n">
-        <v>5.04</v>
+        <v>4.65</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>11010</v>
+        <v>5210</v>
       </c>
       <c r="K14" t="n">
-        <v>10110</v>
+        <v>5220</v>
       </c>
       <c r="L14" t="n">
-        <v>10130</v>
+        <v>5310</v>
       </c>
       <c r="M14" t="n">
-        <v>9870</v>
+        <v>4755</v>
       </c>
       <c r="N14" t="n">
-        <v>5.01</v>
+        <v>4.72</v>
       </c>
       <c r="O14" t="n">
-        <v>3465298520</v>
+        <v>38926627781</v>
       </c>
       <c r="P14" t="n">
-        <v>15900</v>
+        <v>8100</v>
       </c>
       <c r="Q14" t="n">
-        <v>6310</v>
+        <v>592</v>
       </c>
       <c r="R14" t="n">
-        <v>-256000</v>
+        <v>237000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 항생제 회사 주가 급등 언급. 케냐 에볼라, 러시아 관련 부정적 언급.</t>
+          <t>전환사채 발행 및 기타법인의 대량 매도 등 악재성 정보가 언급되며 주가 하락에 대한 우려가 나타남. 단기적인 악재 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['전환사채', '대량매도', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10030</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-8.90%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E15" t="n">
+        <v>66</v>
+      </c>
+      <c r="F15" t="n">
+        <v>49</v>
+      </c>
+      <c r="G15" t="n">
+        <v>263</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9870</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3671900970</v>
+      </c>
+      <c r="P15" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-285000</v>
+      </c>
+      <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>['항생제', '에볼라', '주가 급등']</t>
-        </is>
-      </c>
-      <c r="X14" t="n">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>미국 항생제 보유 회사 주가 상승 소식과 함께 신풍제약에 대한 기대감과 변동성 언급. 향후 주가 전망에 대한 의견 분분.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['항생제', '주가 폭등', '변동성']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>2</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>019170</t>
         </is>
